--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1905-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1905-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{65C0FD78-45E9-4CE8-B0FF-EC4DB24F760F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{18659AD3-D5BF-4D2D-BF04-475108C758F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{989A2044-55D2-4C00-A15D-35E622B6EECE}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{D00B46AF-0E19-45CA-9B11-2C6891442775}"/>
   </bookViews>
   <sheets>
     <sheet name="1905-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1553,29 +1553,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65C30F71-FC2F-47AF-8DBE-12DC7FDE620A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83A1D2F6-122E-4D8B-9016-FE12F0606AA3}">
   <dimension ref="A1:X50"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1609,7 +1608,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1645,7 +1644,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1697,7 +1696,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1765,7 +1764,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1837,7 +1836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>2023</v>
       </c>
@@ -1909,7 +1908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2022</v>
       </c>
@@ -1981,7 +1980,7 @@
         <v>1.89</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="39">
         <v>2021</v>
       </c>
@@ -2053,7 +2052,7 @@
         <v>2.64</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2020</v>
       </c>
@@ -2125,7 +2124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="39">
         <v>2019</v>
       </c>
@@ -2197,7 +2196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>2018</v>
       </c>
@@ -2269,7 +2268,7 @@
         <v>3.96</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="39">
         <v>2017</v>
       </c>
@@ -2341,7 +2340,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2016</v>
       </c>
@@ -2413,7 +2412,7 @@
         <v>3.82</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="39">
         <v>2015</v>
       </c>
@@ -2485,7 +2484,7 @@
         <v>7.03</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="37">
         <v>2014</v>
       </c>
@@ -2557,7 +2556,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <v>2013</v>
       </c>
@@ -2629,7 +2628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <v>2012</v>
       </c>
@@ -2701,7 +2700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="39">
         <v>2011</v>
       </c>
@@ -2773,7 +2772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>2010</v>
       </c>
@@ -2845,7 +2844,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="39">
         <v>2009</v>
       </c>
@@ -2917,7 +2916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <v>2008</v>
       </c>
@@ -2989,7 +2988,7 @@
         <v>1.95</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="39">
         <v>2007</v>
       </c>
@@ -3061,7 +3060,7 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="37">
         <v>2006</v>
       </c>
@@ -3133,7 +3132,7 @@
         <v>4.21</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="39">
         <v>2005</v>
       </c>
@@ -3205,7 +3204,7 @@
         <v>7.93</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>2004</v>
       </c>
@@ -3277,7 +3276,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="41">
         <v>2003</v>
       </c>
@@ -3349,7 +3348,7 @@
         <v>7.55</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="43"/>
       <c r="B27" s="44"/>
       <c r="C27" s="18" t="s">
@@ -3377,7 +3376,7 @@
       <c r="W27" s="50"/>
       <c r="X27" s="46"/>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="51">
         <v>2002</v>
       </c>
@@ -3449,7 +3448,7 @@
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="53"/>
       <c r="B29" s="54"/>
       <c r="C29" s="20" t="s">
@@ -3477,7 +3476,7 @@
       <c r="W29" s="60"/>
       <c r="X29" s="56"/>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="39">
         <v>2001</v>
       </c>
@@ -3549,7 +3548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="37">
         <v>2000</v>
       </c>
@@ -3621,7 +3620,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="39">
         <v>1999</v>
       </c>
@@ -3693,7 +3692,7 @@
         <v>2.94</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="37">
         <v>1998</v>
       </c>
@@ -3765,7 +3764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="39">
         <v>1997</v>
       </c>
@@ -3837,7 +3836,7 @@
         <v>2.94</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="37">
         <v>1996</v>
       </c>
@@ -3909,7 +3908,7 @@
         <v>4.38</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="41">
         <v>1995</v>
       </c>
@@ -3981,7 +3980,7 @@
         <v>7.14</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="43"/>
       <c r="B37" s="44"/>
       <c r="C37" s="18" t="s">
@@ -4009,7 +4008,7 @@
       <c r="W37" s="50"/>
       <c r="X37" s="46"/>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="37">
         <v>1994</v>
       </c>
@@ -4081,7 +4080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="39">
         <v>1993</v>
       </c>
@@ -4153,7 +4152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="37">
         <v>1992</v>
       </c>
@@ -4225,7 +4224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="39">
         <v>1991</v>
       </c>
@@ -4297,7 +4296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="37">
         <v>1990</v>
       </c>
@@ -4369,7 +4368,7 @@
         <v>2.37</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="41">
         <v>1989</v>
       </c>
@@ -4441,7 +4440,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="43"/>
       <c r="B44" s="44"/>
       <c r="C44" s="18" t="s">
@@ -4469,7 +4468,7 @@
       <c r="W44" s="50"/>
       <c r="X44" s="46"/>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="37">
         <v>1988</v>
       </c>
@@ -4541,7 +4540,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="39">
         <v>1987</v>
       </c>
@@ -4613,7 +4612,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="37">
         <v>1986</v>
       </c>
@@ -4685,7 +4684,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="39">
         <v>1984</v>
       </c>
@@ -4757,7 +4756,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="37">
         <v>1983</v>
       </c>
@@ -4829,7 +4828,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="39" t="s">
         <v>53</v>
       </c>
